--- a/artfynd/A 65914-2021 artfynd.xlsx
+++ b/artfynd/A 65914-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126221187</v>
       </c>
       <c r="B2" t="n">
-        <v>57563</v>
+        <v>57567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65914-2021 artfynd.xlsx
+++ b/artfynd/A 65914-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126221187</v>
       </c>
       <c r="B2" t="n">
-        <v>57567</v>
+        <v>57568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
